--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -64,7 +64,7 @@
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="13" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24" style="5" customWidth="1"/>
     <col min="4" max="4" width="17" style="6" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -65,7 +65,7 @@
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="24" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17" style="6" customWidth="1"/>
+    <col min="4" max="4" width="18" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
+++ b/src/Excelsior.Tests/DictionarySheetTests.Basic.verified.xlsx
@@ -64,8 +64,8 @@
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="13" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17" style="6" customWidth="1"/>
+    <col min="3" max="3" width="24" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
